--- a/Tagihan/2026/Agustus/Kasiau.xlsx
+++ b/Tagihan/2026/Agustus/Kasiau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3491542-10F7-4AE3-A427-677908D6AE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50A69BC-1E89-4670-99AF-A2CE923BD453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>NO.</t>
   </si>
@@ -88,6 +88,27 @@
   </si>
   <si>
     <t>Lot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kepada Tuan/Nyonya  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabel Fiber Optik </t>
+  </si>
+  <si>
+    <t>Swith Hub</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>HTB</t>
+  </si>
+  <si>
+    <t>Kabel Listrik + Material</t>
+  </si>
+  <si>
+    <t>Mobilisasi</t>
   </si>
   <si>
     <r>
@@ -101,11 +122,11 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>04 September 2026</t>
+      <t>09 September 2026</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Kepada Tuan/Nyonya  </t>
+    <t>Reset dan Konfigurasi Ulang</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1066,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="47" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G13" s="47"/>
     </row>
@@ -1055,7 +1076,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="48"/>
     </row>
@@ -1097,11 +1118,11 @@
         <v>18</v>
       </c>
       <c r="F17" s="15">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G17" s="15">
-        <f t="shared" ref="G17:G18" si="0">F17*D17</f>
-        <v>200000</v>
+        <f t="shared" ref="G17:G24" si="0">F17*D17</f>
+        <v>300000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1126,52 +1147,129 @@
       </c>
     </row>
     <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="B19" s="25">
+        <v>3</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="2">
+        <v>200</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350000</v>
+      </c>
+      <c r="G19" s="15">
+        <v>350000</v>
+      </c>
     </row>
     <row r="20" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="15"/>
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="14">
+        <v>150000</v>
+      </c>
+      <c r="G20" s="15">
+        <f>F20*D20</f>
+        <v>150000</v>
+      </c>
     </row>
     <row r="21" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="15"/>
+      <c r="B21" s="25">
+        <v>5</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="14">
+        <v>150000</v>
+      </c>
+      <c r="G21" s="15">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
     </row>
     <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="16"/>
+      <c r="B22" s="2">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="14">
+        <v>50000</v>
+      </c>
+      <c r="G22" s="15">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
     </row>
     <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="16"/>
+      <c r="B23" s="25">
+        <v>7</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="14">
+        <v>50000</v>
+      </c>
+      <c r="G23" s="15">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
     </row>
     <row r="24" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="16"/>
+      <c r="B24" s="2">
+        <v>8</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="14">
+        <v>50000</v>
+      </c>
+      <c r="G24" s="16">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
     </row>
     <row r="25" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
@@ -1207,7 +1305,7 @@
       <c r="F28" s="44"/>
       <c r="G28" s="18">
         <f>SUM(G17:G27)</f>
-        <v>825000</v>
+        <v>1725000</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
